--- a/vse-loti/340021881/spec-340021881.xlsx
+++ b/vse-loti/340021881/spec-340021881.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -453,35 +453,40 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Наименование позиции (⌀ + s, если указано)</t>
+          <t>Наименование позиции</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>D×s, мм</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Кол-во (исх.)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ед. изм.</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Масса, т (приведённая)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
         </is>
@@ -500,7 +505,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="G3" s="3" t="n">
         <v>1611800</v>
       </c>
     </row>
